--- a/docs/perechen-otchetov/obrazcy/ФО-24.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-24.xlsx
@@ -2502,7 +2502,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="90" customHeight="1">
+    <row r="34" ht="75" customHeight="1">
       <c r="A34" s="25" t="inlineStr">
         <is>
           <t>2.</t>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>Остаток на конец в ИТОГО = остаток основного долга всего портфеля на 30.09.2026: ИТОГО ФО-02 «по основной сумме» 67 729,500 + КЗ-25 7 308,000 (в образце ФО-02 его нет). Изменение = выдано 1 500,000 (КЗ-17) − погашено по основной сумме 1 467,000 (ФО-04) − списано 750,000 (ФО-11) + курсовая разница 116,500 (КЗ-11 17,500 — как в ФО-53, КЗ-21 36,000, КЗ-22 14,400, КЗ-23 27,000, КЗ-25 21,600); перевод долга КЗ-07 итог не меняет: −2 650,000 у прежнего заёмщика и +2 650,000 у нового.</t>
+          <t>Остаток на конец в ИТОГО = остаток основного долга всего портфеля на 30.09.2026: ИТОГО ФО-02 «по основной сумме» 75 037,500 (в том числе КЗ-25 7 308,000). Изменение = выдано 1 500,000 (КЗ-17) − погашено по основной сумме 1 467,000 (ФО-04) − списано 750,000 (ФО-11) + курсовая разница 116,500 (КЗ-11 17,500 — как в ФО-53, КЗ-21 36,000, КЗ-22 14,400, КЗ-23 27,000, КЗ-25 21,600); перевод долга КЗ-07 итог не меняет: −2 650,000 у прежнего заёмщика и +2 650,000 у нового.</t>
         </is>
       </c>
     </row>
